--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T10:41:09+00:00</t>
+    <t>2026-08-27T11:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:11:54+00:00</t>
+    <t>2026-08-27T11:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:29:36+00:00</t>
+    <t>2026-08-27T12:06:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:06:00+00:00</t>
+    <t>2026-08-27T15:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:31:43+00:00</t>
+    <t>2026-08-27T15:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:57:15+00:00</t>
+    <t>2026-08-28T06:12:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:12:02+00:00</t>
+    <t>2026-08-28T06:31:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:31:49+00:00</t>
+    <t>2026-08-28T06:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:49:57+00:00</t>
+    <t>2026-08-28T07:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:24:31+00:00</t>
+    <t>2026-08-28T07:40:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:40:52+00:00</t>
+    <t>2026-08-28T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:03:44+00:00</t>
+    <t>2026-08-28T09:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:05:47+00:00</t>
+    <t>2026-08-28T09:25:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:25:31+00:00</t>
+    <t>2026-08-28T09:53:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:53:30+00:00</t>
+    <t>2026-08-28T10:16:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:16:47+00:00</t>
+    <t>2026-08-28T12:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:10:16+00:00</t>
+    <t>2026-08-28T12:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:26:30+00:00</t>
+    <t>2026-08-28T12:47:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:47:27+00:00</t>
+    <t>2026-08-28T13:10:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:10:09+00:00</t>
+    <t>2026-08-28T13:33:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:33:24+00:00</t>
+    <t>2026-08-28T13:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:57:18+00:00</t>
+    <t>2026-08-28T14:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:33:40+00:00</t>
+    <t>2026-08-28T14:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:57:41+00:00</t>
+    <t>2026-08-28T15:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:24:04+00:00</t>
+    <t>2026-08-28T15:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:48:09+00:00</t>
+    <t>2026-08-28T18:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T18:25:22+00:00</t>
+    <t>2026-08-28T19:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T19:18:26+00:00</t>
+    <t>2026-08-31T13:44:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:44:47+00:00</t>
+    <t>2026-08-31T14:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$174</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6326" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6673" uniqueCount="702">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:28:40+00:00</t>
+    <t>2026-08-31T15:22:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2088,6 +2088,10 @@
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:code}
+</t>
+  </si>
+  <si>
     <t>containment by OBX-4?</t>
   </si>
   <si>
@@ -2161,6 +2165,57 @@
   </si>
   <si>
     <t>Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
+  </si>
+  <si>
+    <t>Observation.component:multipleTumoren</t>
+  </si>
+  <si>
+    <t>multipleTumoren</t>
+  </si>
+  <si>
+    <t>Multiple Primaertumoren als m-Suffix</t>
+  </si>
+  <si>
+    <t>Multiple Primaertumoren in einem anatomischen Bezirk nach 8.10 oBDS 2021 - UICC-m-Suffix der T-Kategorie</t>
+  </si>
+  <si>
+    <t>Observation.component:multipleTumoren.id</t>
+  </si>
+  <si>
+    <t>Observation.component:multipleTumoren.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:multipleTumoren.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:multipleTumoren.code</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="42030-7"/&gt;
+    &lt;display value="Multiple tumors reported as single primary Cancer"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Observation.component:multipleTumoren.value[x]</t>
+  </si>
+  <si>
+    <t>(m) = multiple Tumoren ohne Angabe der Zahl; (2)/(3)/(4) = Anzahl der multiplen Tumoren; nicht angegeben = keine multiplen Tumoren. Fuer die reine Mehrfachigkeit existiert in SNOMED CT das Qualifier-Konzept 369755005 |Multiple tumors|; fuer die Zaehlvarianten gibt es keine Entsprechung, daher hier kein Dual-Coding.</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/ValueSet/mii-vs-onko-tnm-m-symbol</t>
+  </si>
+  <si>
+    <t>Observation.component:multipleTumoren.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Observation.component:multipleTumoren.interpretation</t>
+  </si>
+  <si>
+    <t>Observation.component:multipleTumoren.referenceRange</t>
   </si>
 </sst>
 </file>
@@ -2477,12 +2532,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP165"/>
+  <dimension ref="A1:AP174"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.59375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="48.65625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.37109375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -21346,16 +21401,14 @@
         <v>82</v>
       </c>
       <c r="AB157" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC157" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>662</v>
+      </c>
+      <c r="AC157" s="2"/>
       <c r="AD157" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE157" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AF157" t="s" s="2">
         <v>657</v>
@@ -21382,7 +21435,7 @@
         <v>82</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>82</v>
@@ -21393,10 +21446,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21511,10 +21564,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21631,10 +21684,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21753,10 +21806,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21782,13 +21835,13 @@
         <v>215</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="O161" t="s" s="2">
         <v>378</v>
@@ -21819,10 +21872,10 @@
         <v>157</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="Z161" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>82</v>
@@ -21840,7 +21893,7 @@
         <v>82</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>92</v>
@@ -21861,7 +21914,7 @@
         <v>82</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AN161" t="s" s="2">
         <v>382</v>
@@ -21875,10 +21928,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -21901,16 +21954,16 @@
         <v>93</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="M162" t="s" s="2">
         <v>487</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="O162" t="s" s="2">
         <v>489</v>
@@ -21962,7 +22015,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -21983,7 +22036,7 @@
         <v>82</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>492</v>
@@ -21997,10 +22050,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22026,13 +22079,13 @@
         <v>215</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="O163" t="s" s="2">
         <v>536</v>
@@ -22084,7 +22137,7 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -22119,10 +22172,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22206,7 +22259,7 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -22241,10 +22294,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22270,10 +22323,10 @@
         <v>83</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="N165" t="s" s="2">
         <v>601</v>
@@ -22328,7 +22381,7 @@
         <v>82</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22361,8 +22414,1100 @@
         <v>82</v>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="C166" t="s" s="2">
+        <v>688</v>
+      </c>
+      <c r="D166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E166" s="2"/>
+      <c r="F166" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G166" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H166" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="I166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J166" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K166" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="L166" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="M166" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="N166" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="O166" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="P166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q166" s="2"/>
+      <c r="R166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF166" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="AG166" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH166" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ166" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN166" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AO166" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP166" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="167" hidden="true">
+      <c r="A167" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="C167" s="2"/>
+      <c r="D167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E167" s="2"/>
+      <c r="F167" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G167" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K167" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L167" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="M167" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N167" s="2"/>
+      <c r="O167" s="2"/>
+      <c r="P167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q167" s="2"/>
+      <c r="R167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF167" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG167" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH167" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO167" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP167" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="168" hidden="true">
+      <c r="A168" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="C168" s="2"/>
+      <c r="D168" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E168" s="2"/>
+      <c r="F168" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G168" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K168" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L168" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M168" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O168" s="2"/>
+      <c r="P168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q168" s="2"/>
+      <c r="R168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF168" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG168" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH168" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ168" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO168" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP168" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="169" hidden="true">
+      <c r="A169" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="C169" s="2"/>
+      <c r="D169" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="E169" s="2"/>
+      <c r="F169" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G169" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I169" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="J169" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K169" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L169" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M169" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="N169" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O169" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="P169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q169" s="2"/>
+      <c r="R169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF169" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AG169" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH169" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ169" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO169" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP169" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="170" hidden="true">
+      <c r="A170" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="C170" s="2"/>
+      <c r="D170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E170" s="2"/>
+      <c r="F170" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G170" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J170" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K170" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L170" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="M170" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="N170" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="O170" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="P170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q170" s="2"/>
+      <c r="R170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S170" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="T170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X170" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="Y170" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="Z170" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="AA170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF170" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AG170" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH170" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ170" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM170" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="AN170" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AO170" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AP170" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="171" hidden="true">
+      <c r="A171" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="C171" s="2"/>
+      <c r="D171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E171" s="2"/>
+      <c r="F171" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G171" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J171" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K171" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L171" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="M171" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="N171" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="O171" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="P171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q171" s="2"/>
+      <c r="R171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X171" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="Y171" s="2"/>
+      <c r="Z171" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="AA171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF171" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="AG171" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH171" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ171" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM171" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="AN171" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AO171" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP171" t="s" s="2">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="172" hidden="true">
+      <c r="A172" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="C172" s="2"/>
+      <c r="D172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E172" s="2"/>
+      <c r="F172" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G172" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K172" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L172" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="M172" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="N172" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="O172" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="P172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q172" s="2"/>
+      <c r="R172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X172" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="Y172" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="Z172" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AA172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF172" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="AG172" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH172" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI172" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AJ172" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN172" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AO172" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP172" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="173" hidden="true">
+      <c r="A173" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="C173" s="2"/>
+      <c r="D173" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="E173" s="2"/>
+      <c r="F173" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K173" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L173" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M173" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N173" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="O173" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="P173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q173" s="2"/>
+      <c r="R173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X173" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="Y173" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="Z173" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AA173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF173" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="AG173" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH173" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ173" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM173" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AN173" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AO173" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP173" t="s" s="2">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="174" hidden="true">
+      <c r="A174" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="C174" s="2"/>
+      <c r="D174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E174" s="2"/>
+      <c r="F174" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K174" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L174" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="M174" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="O174" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="P174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q174" s="2"/>
+      <c r="R174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF174" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="AG174" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH174" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ174" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN174" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AO174" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP174" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AP165">
+  <autoFilter ref="A1:AP174">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -22372,7 +23517,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI164">
+  <conditionalFormatting sqref="A2:AI173">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:22:09+00:00</t>
+    <t>2026-09-01T08:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:53:35+00:00</t>
+    <t>2026-09-01T09:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:38:31+00:00</t>
+    <t>2026-09-01T11:08:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:08:21+00:00</t>
+    <t>2026-09-01T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:29:01+00:00</t>
+    <t>2026-09-01T19:43:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:43:49+00:00</t>
+    <t>2026-09-01T20:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:38:11+00:00</t>
+    <t>2026-09-01T21:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tnm-t-kategorie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:24:42+00:00</t>
+    <t>2026-09-01T22:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
